--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_006.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_006.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="137">
   <si>
     <t>Sezione</t>
   </si>
@@ -330,6 +330,12 @@
   </si>
   <si>
     <t>evento.trascrizioneNascita.tipoRichiedente,=,3</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>evento.trascrizioneNascita.tipoRichiedente,!=,3</t>
@@ -475,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H230"/>
+  <dimension ref="A1:H232"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.71875" customWidth="true" bestFit="true"/>
@@ -4816,22 +4822,22 @@
         <v>103</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="190">
@@ -4839,7 +4845,7 @@
         <v>103</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>13</v>
@@ -4848,13 +4854,13 @@
         <v>104</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F190" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="191">
@@ -4862,22 +4868,22 @@
         <v>103</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="192">
@@ -4885,22 +4891,22 @@
         <v>103</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="193">
@@ -4908,7 +4914,7 @@
         <v>103</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>13</v>
@@ -4917,13 +4923,13 @@
         <v>104</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F193" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="194">
@@ -4931,7 +4937,7 @@
         <v>103</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>13</v>
@@ -4940,13 +4946,13 @@
         <v>104</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="195">
@@ -4954,7 +4960,7 @@
         <v>103</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>13</v>
@@ -4963,13 +4969,13 @@
         <v>104</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="196">
@@ -4977,22 +4983,22 @@
         <v>103</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F196" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="197">
@@ -5000,7 +5006,7 @@
         <v>103</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>9</v>
@@ -5009,13 +5015,13 @@
         <v>104</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="198">
@@ -5023,7 +5029,7 @@
         <v>103</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>9</v>
@@ -5032,13 +5038,13 @@
         <v>104</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="199">
@@ -5046,7 +5052,7 @@
         <v>103</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>9</v>
@@ -5055,13 +5061,13 @@
         <v>104</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="200">
@@ -5069,7 +5075,7 @@
         <v>103</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>9</v>
@@ -5078,13 +5084,13 @@
         <v>104</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="201">
@@ -5092,7 +5098,7 @@
         <v>103</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>9</v>
@@ -5101,13 +5107,13 @@
         <v>104</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="202">
@@ -5115,7 +5121,7 @@
         <v>103</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>9</v>
@@ -5124,13 +5130,13 @@
         <v>104</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="203">
@@ -5138,7 +5144,7 @@
         <v>103</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>9</v>
@@ -5147,13 +5153,13 @@
         <v>104</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="204">
@@ -5161,7 +5167,7 @@
         <v>103</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>9</v>
@@ -5170,13 +5176,13 @@
         <v>104</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="205">
@@ -5184,7 +5190,7 @@
         <v>103</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>9</v>
@@ -5193,13 +5199,13 @@
         <v>104</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="206">
@@ -5207,7 +5213,7 @@
         <v>103</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>9</v>
@@ -5216,13 +5222,13 @@
         <v>104</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="207">
@@ -5230,7 +5236,7 @@
         <v>103</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>9</v>
@@ -5239,13 +5245,13 @@
         <v>104</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="208">
@@ -5253,7 +5259,7 @@
         <v>103</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>9</v>
@@ -5262,13 +5268,13 @@
         <v>104</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="209">
@@ -5276,7 +5282,7 @@
         <v>103</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>9</v>
@@ -5285,13 +5291,13 @@
         <v>104</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="210">
@@ -5299,7 +5305,7 @@
         <v>103</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>9</v>
@@ -5308,13 +5314,13 @@
         <v>104</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="211">
@@ -5322,7 +5328,7 @@
         <v>103</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>9</v>
@@ -5331,13 +5337,13 @@
         <v>104</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="212">
@@ -5345,22 +5351,22 @@
         <v>103</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="213">
@@ -5368,22 +5374,22 @@
         <v>103</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="214">
@@ -5391,22 +5397,22 @@
         <v>103</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="215">
@@ -5414,22 +5420,22 @@
         <v>103</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="216">
@@ -5437,7 +5443,7 @@
         <v>103</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>9</v>
@@ -5446,13 +5452,13 @@
         <v>104</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="217">
@@ -5460,7 +5466,7 @@
         <v>103</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>9</v>
@@ -5469,13 +5475,13 @@
         <v>104</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="218">
@@ -5483,7 +5489,7 @@
         <v>103</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>9</v>
@@ -5492,76 +5498,76 @@
         <v>104</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B219" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G219" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F219" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G219" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E220" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B220" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="F220" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C221" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F221" s="2" t="s">
         <v>10</v>
@@ -5572,19 +5578,19 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>10</v>
@@ -5595,19 +5601,19 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>10</v>
@@ -5618,19 +5624,19 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>10</v>
@@ -5641,19 +5647,19 @@
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>10</v>
@@ -5664,19 +5670,19 @@
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>10</v>
@@ -5687,19 +5693,19 @@
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B227" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B227" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="C227" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>10</v>
@@ -5710,19 +5716,19 @@
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>10</v>
@@ -5733,19 +5739,19 @@
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>10</v>
@@ -5756,24 +5762,70 @@
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B230" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B230" s="2" t="s">
+      <c r="C230" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C230" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E230" s="2" t="s">
+      <c r="C231" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E231" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F230" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G230" s="2" t="s">
+      <c r="F231" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G232" s="2" t="s">
         <v>22</v>
       </c>
     </row>
